--- a/SUPERVISORS.xlsx
+++ b/SUPERVISORS.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WESTEN GROUP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WESTEN GROUP\Desktop\telegram_bot-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A236AA8D-F6B3-4335-9049-D2E16AF0CCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE42C068-8E4B-46E7-A44D-9E29A16F3665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4176" yWindow="3984" windowWidth="17280" windowHeight="9036" xr2:uid="{66269D5D-9CEF-4F08-BE66-098B984FB84B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{66269D5D-9CEF-4F08-BE66-098B984FB84B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,8 +38,70 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>HP</author>
+  </authors>
+  <commentList>
+    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{543BABC2-9AF7-4A49-9B0A-70B61631CC48}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{FAB32FE1-D766-4C75-B2C1-3C88FE6E2C02}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="540">
   <si>
     <t>ULSTP0101</t>
   </si>
@@ -1389,9 +1450,6 @@
     <t>jd</t>
   </si>
   <si>
-    <t>JD0101</t>
-  </si>
-  <si>
     <t>JD0102</t>
   </si>
   <si>
@@ -1618,6 +1676,51 @@
   </si>
   <si>
     <t>JD9502</t>
+  </si>
+  <si>
+    <t>JDS0101</t>
+  </si>
+  <si>
+    <t>JDS0102</t>
+  </si>
+  <si>
+    <t>JDS0103</t>
+  </si>
+  <si>
+    <t>JD0116</t>
+  </si>
+  <si>
+    <t>JDS0104</t>
+  </si>
+  <si>
+    <t>JDS1001</t>
+  </si>
+  <si>
+    <t>JDS1002</t>
+  </si>
+  <si>
+    <t>JDS5001</t>
+  </si>
+  <si>
+    <t>JDS4001</t>
+  </si>
+  <si>
+    <t>JDS6001</t>
+  </si>
+  <si>
+    <t>JDS3001</t>
+  </si>
+  <si>
+    <t>JDS7001</t>
+  </si>
+  <si>
+    <t>JDS8001</t>
+  </si>
+  <si>
+    <t>JDS8501</t>
+  </si>
+  <si>
+    <t>JDS9001</t>
   </si>
 </sst>
 </file>
@@ -1631,7 +1734,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _₸_-;\-* #,##0.00\ _₸_-;_-* &quot;-&quot;??\ _₸_-;_-@_-"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -1909,8 +2012,51 @@
       <family val="1"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <charset val="204"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <charset val="204"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2137,8 +2283,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2402,6 +2554,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1510">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3928,7 +4128,7 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3966,14 +4166,34 @@
     <xf numFmtId="0" fontId="3" fillId="35" borderId="12" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="35" borderId="18" xfId="1504" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="1504" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="37" borderId="18" xfId="1504" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="22" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="18" xfId="1504" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="22" xfId="1504" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="23" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="23" xfId="1504" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="1504" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="41" borderId="24" xfId="1504" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="1504" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="1504" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="24" xfId="1504" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="42" fillId="41" borderId="24" xfId="1504" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1510">
     <cellStyle name="20% — акцент1 2" xfId="1391" xr:uid="{DECD8008-35E6-46CA-B1F0-84B8E5FB8850}"/>
@@ -5487,7 +5707,137 @@
     <cellStyle name="Финансовый 9 2" xfId="1508" xr:uid="{90C4B25E-CF13-4ED1-A43F-A8DBC0BC1F44}"/>
     <cellStyle name="Хороший 2" xfId="1374" xr:uid="{B751DBD5-5C97-4376-86B6-FB1A34545A07}"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5897,8 +6247,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12B37F5-AC02-48CA-B5FD-3AA1F9B6D347}">
-  <dimension ref="A1:M93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12B37F5-AC02-48CA-B5FD-3AA1F9B6D347}">
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
@@ -5945,14 +6295,14 @@
       <c r="G3" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="M3" s="14" t="s">
-        <v>449</v>
+      <c r="M3" s="15" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -5968,14 +6318,14 @@
       <c r="G4" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="M4" s="14" t="s">
-        <v>450</v>
+      <c r="M4" s="16" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -5991,14 +6341,14 @@
       <c r="G5" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="M5" s="14" t="s">
-        <v>451</v>
+      <c r="M5" s="16" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -6014,14 +6364,14 @@
       <c r="G6" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="M6" s="14" t="s">
-        <v>452</v>
+      <c r="M6" s="16" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -6037,14 +6387,14 @@
       <c r="G7" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="M7" s="14" t="s">
-        <v>453</v>
+      <c r="M7" s="16" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -6060,14 +6410,14 @@
       <c r="G8" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="M8" s="14" t="s">
-        <v>454</v>
+      <c r="M8" s="16" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -6083,14 +6433,14 @@
       <c r="G9" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="M9" s="14" t="s">
-        <v>455</v>
+      <c r="M9" s="16" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -6106,14 +6456,14 @@
       <c r="G10" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="M10" s="14" t="s">
-        <v>456</v>
+      <c r="M10" s="15" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -6129,14 +6479,14 @@
       <c r="G11" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="M11" s="14" t="s">
-        <v>457</v>
+      <c r="M11" s="17" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -6152,14 +6502,14 @@
       <c r="G12" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="M12" s="14" t="s">
-        <v>458</v>
+      <c r="M12" s="17" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -6175,14 +6525,14 @@
       <c r="G13" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="M13" s="14" t="s">
-        <v>459</v>
+      <c r="M13" s="17" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -6198,14 +6548,14 @@
       <c r="G14" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="M14" s="14" t="s">
-        <v>460</v>
+      <c r="M14" s="16" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -6221,14 +6571,14 @@
       <c r="G15" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="M15" s="14" t="s">
-        <v>461</v>
+      <c r="M15" s="16" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -6244,14 +6594,14 @@
       <c r="G16" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="M16" s="14" t="s">
-        <v>462</v>
+      <c r="M16" s="15" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -6267,14 +6617,14 @@
       <c r="G17" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="M17" s="14" t="s">
-        <v>463</v>
+      <c r="M17" s="17" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -6290,14 +6640,14 @@
       <c r="G18" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="M18" s="14" t="s">
-        <v>464</v>
+      <c r="M18" s="17" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -6313,14 +6663,14 @@
       <c r="G19" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="M19" s="14" t="s">
-        <v>465</v>
+      <c r="M19" s="17" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -6336,14 +6686,14 @@
       <c r="G20" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="M20" s="14" t="s">
-        <v>466</v>
+      <c r="M20" s="17" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -6359,14 +6709,14 @@
       <c r="G21" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="M21" s="14" t="s">
-        <v>467</v>
+      <c r="M21" s="17" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -6382,14 +6732,14 @@
       <c r="G22" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="K22" s="15" t="s">
+      <c r="K22" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="M22" s="14" t="s">
-        <v>468</v>
+      <c r="M22" s="15" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -6405,14 +6755,14 @@
       <c r="G23" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="K23" s="15" t="s">
+      <c r="K23" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="M23" s="14" t="s">
-        <v>469</v>
+      <c r="M23" s="17" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -6428,14 +6778,14 @@
       <c r="G24" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="K24" s="15" t="s">
+      <c r="K24" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="M24" s="14" t="s">
-        <v>470</v>
+      <c r="M24" s="17" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -6451,14 +6801,14 @@
       <c r="G25" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="M25" s="14" t="s">
-        <v>471</v>
+      <c r="M25" s="17" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -6474,14 +6824,14 @@
       <c r="G26" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="K26" s="15" t="s">
+      <c r="K26" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="M26" s="14" t="s">
-        <v>472</v>
+      <c r="M26" s="17" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -6497,14 +6847,14 @@
       <c r="G27" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="M27" s="14" t="s">
-        <v>473</v>
+      <c r="M27" s="17" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -6520,14 +6870,14 @@
       <c r="G28" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="M28" s="14" t="s">
-        <v>474</v>
+      <c r="M28" s="15" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
@@ -6543,14 +6893,14 @@
       <c r="G29" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="M29" s="14" t="s">
-        <v>475</v>
+      <c r="M29" s="17" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -6566,14 +6916,14 @@
       <c r="G30" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="K30" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="M30" s="14" t="s">
-        <v>476</v>
+      <c r="M30" s="17" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
@@ -6589,14 +6939,14 @@
       <c r="G31" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="M31" s="14" t="s">
-        <v>477</v>
+      <c r="M31" s="17" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
@@ -6612,14 +6962,14 @@
       <c r="G32" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="M32" s="14" t="s">
-        <v>478</v>
+      <c r="M32" s="17" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
@@ -6635,14 +6985,14 @@
       <c r="G33" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="K33" s="15" t="s">
+      <c r="K33" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="M33" s="14" t="s">
-        <v>479</v>
+      <c r="M33" s="17" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
@@ -6658,14 +7008,14 @@
       <c r="G34" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="K34" s="15" t="s">
+      <c r="K34" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="M34" s="14" t="s">
-        <v>480</v>
+      <c r="M34" s="15" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
@@ -6681,14 +7031,14 @@
       <c r="G35" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="K35" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="M35" s="14" t="s">
-        <v>481</v>
+      <c r="M35" s="17" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
@@ -6704,14 +7054,14 @@
       <c r="G36" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="K36" s="15" t="s">
+      <c r="K36" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="M36" s="14" t="s">
-        <v>482</v>
+      <c r="M36" s="17" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
@@ -6727,14 +7077,14 @@
       <c r="G37" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="K37" s="15" t="s">
+      <c r="K37" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="M37" s="14" t="s">
-        <v>483</v>
+      <c r="M37" s="17" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
@@ -6750,14 +7100,14 @@
       <c r="G38" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="K38" s="15" t="s">
+      <c r="K38" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="M38" s="14" t="s">
-        <v>484</v>
+      <c r="M38" s="17" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
@@ -6773,14 +7123,14 @@
       <c r="G39" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="K39" s="15" t="s">
+      <c r="K39" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="M39" s="14" t="s">
-        <v>485</v>
+      <c r="M39" s="17" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
@@ -6796,14 +7146,14 @@
       <c r="G40" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="K40" s="15" t="s">
+      <c r="K40" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="M40" s="14" t="s">
-        <v>486</v>
+      <c r="M40" s="18" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -6819,14 +7169,14 @@
       <c r="G41" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="K41" s="15" t="s">
+      <c r="K41" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="M41" s="14" t="s">
-        <v>487</v>
+      <c r="M41" s="19" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
@@ -6842,14 +7192,14 @@
       <c r="G42" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="K42" s="15" t="s">
+      <c r="K42" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="M42" s="14" t="s">
-        <v>488</v>
+      <c r="M42" s="19" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
@@ -6865,14 +7215,14 @@
       <c r="G43" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="K43" s="15" t="s">
+      <c r="K43" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="M43" s="14" t="s">
-        <v>489</v>
+      <c r="M43" s="19" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
@@ -6888,14 +7238,14 @@
       <c r="G44" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="K44" s="15" t="s">
+      <c r="K44" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="M44" s="14" t="s">
-        <v>490</v>
+      <c r="M44" s="20" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
@@ -6911,14 +7261,14 @@
       <c r="G45" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="I45" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="K45" s="15" t="s">
+      <c r="K45" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="M45" s="14" t="s">
-        <v>491</v>
+      <c r="M45" s="18" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -6934,14 +7284,14 @@
       <c r="G46" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I46" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="K46" s="15" t="s">
+      <c r="K46" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="M46" s="14" t="s">
-        <v>492</v>
+      <c r="M46" s="21" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
@@ -6957,14 +7307,14 @@
       <c r="G47" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="K47" s="15" t="s">
+      <c r="K47" s="13" t="s">
         <v>427</v>
       </c>
-      <c r="M47" s="14" t="s">
-        <v>493</v>
+      <c r="M47" s="21" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
@@ -6980,14 +7330,14 @@
       <c r="G48" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="K48" s="15" t="s">
+      <c r="K48" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="M48" s="14" t="s">
-        <v>494</v>
+      <c r="M48" s="21" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
@@ -7003,14 +7353,14 @@
       <c r="G49" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="I49" s="15" t="s">
+      <c r="I49" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="K49" s="15" t="s">
+      <c r="K49" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="M49" s="14" t="s">
-        <v>495</v>
+      <c r="M49" s="21" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
@@ -7026,14 +7376,14 @@
       <c r="G50" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="I50" s="15" t="s">
+      <c r="I50" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="K50" s="15" t="s">
+      <c r="K50" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="M50" s="14" t="s">
-        <v>496</v>
+      <c r="M50" s="21" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
@@ -7049,14 +7399,14 @@
       <c r="G51" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="I51" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="K51" s="15" t="s">
+      <c r="K51" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="M51" s="14" t="s">
-        <v>497</v>
+      <c r="M51" s="22" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
@@ -7072,14 +7422,14 @@
       <c r="G52" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="I52" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="K52" s="15" t="s">
+      <c r="K52" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="M52" s="14" t="s">
-        <v>498</v>
+      <c r="M52" s="18" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
@@ -7095,14 +7445,14 @@
       <c r="G53" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="I53" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="K53" s="16" t="s">
+      <c r="K53" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="M53" s="14" t="s">
-        <v>499</v>
+      <c r="M53" s="23" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
@@ -7118,14 +7468,14 @@
       <c r="G54" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="I54" s="15" t="s">
+      <c r="I54" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="K54" s="15" t="s">
+      <c r="K54" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="M54" s="14" t="s">
-        <v>500</v>
+      <c r="M54" s="23" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
@@ -7141,14 +7491,14 @@
       <c r="G55" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I55" s="15" t="s">
+      <c r="I55" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="K55" s="15" t="s">
+      <c r="K55" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="M55" s="14" t="s">
-        <v>501</v>
+      <c r="M55" s="23" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
@@ -7164,14 +7514,14 @@
       <c r="G56" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="I56" s="15" t="s">
+      <c r="I56" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="K56" s="15" t="s">
+      <c r="K56" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="M56" s="14" t="s">
-        <v>502</v>
+      <c r="M56" s="20" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
@@ -7187,14 +7537,14 @@
       <c r="G57" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="I57" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="K57" s="15" t="s">
+      <c r="K57" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="M57" s="14" t="s">
-        <v>503</v>
+      <c r="M57" s="15" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
@@ -7210,14 +7560,14 @@
       <c r="G58" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="I58" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="K58" s="15" t="s">
+      <c r="K58" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="M58" s="14" t="s">
-        <v>504</v>
+      <c r="M58" s="24" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
@@ -7233,14 +7583,14 @@
       <c r="G59" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="I59" s="15" t="s">
+      <c r="I59" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="K59" s="15" t="s">
+      <c r="K59" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="M59" s="13" t="s">
-        <v>505</v>
+      <c r="M59" s="25" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
@@ -7256,14 +7606,14 @@
       <c r="G60" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="I60" s="15" t="s">
+      <c r="I60" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="K60" s="15" t="s">
+      <c r="K60" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="M60" s="14" t="s">
-        <v>506</v>
+      <c r="M60" s="26" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
@@ -7279,14 +7629,14 @@
       <c r="G61" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="I61" s="15" t="s">
+      <c r="I61" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="K61" s="15" t="s">
+      <c r="K61" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="M61" s="14" t="s">
-        <v>507</v>
+      <c r="M61" s="27" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
@@ -7302,14 +7652,14 @@
       <c r="G62" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="I62" s="15" t="s">
+      <c r="I62" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="K62" s="15" t="s">
+      <c r="K62" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="M62" s="14" t="s">
-        <v>508</v>
+      <c r="M62" s="25" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
@@ -7325,14 +7675,14 @@
       <c r="G63" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="I63" s="15" t="s">
+      <c r="I63" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="K63" s="15" t="s">
+      <c r="K63" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="M63" s="14" t="s">
-        <v>509</v>
+      <c r="M63" s="15" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
@@ -7348,14 +7698,14 @@
       <c r="G64" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="I64" s="15" t="s">
+      <c r="I64" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K64" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="M64" s="14" t="s">
-        <v>510</v>
+      <c r="M64" s="24" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
@@ -7371,14 +7721,14 @@
       <c r="G65" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="I65" s="15" t="s">
+      <c r="I65" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="K65" s="15" t="s">
+      <c r="K65" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="M65" s="14" t="s">
-        <v>511</v>
+      <c r="M65" s="24" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
@@ -7394,11 +7744,11 @@
       <c r="G66" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="K66" s="15" t="s">
+      <c r="K66" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="M66" s="14" t="s">
-        <v>512</v>
+      <c r="M66" s="24" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
@@ -7414,11 +7764,11 @@
       <c r="G67" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="K67" s="15" t="s">
+      <c r="K67" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="M67" s="14" t="s">
-        <v>513</v>
+      <c r="M67" s="24" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
@@ -7434,8 +7784,8 @@
       <c r="G68" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="M68" s="13" t="s">
-        <v>514</v>
+      <c r="M68" s="15" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.35">
@@ -7448,8 +7798,8 @@
       <c r="E69" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="M69" s="14" t="s">
-        <v>515</v>
+      <c r="M69" s="24" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.35">
@@ -7462,8 +7812,8 @@
       <c r="E70" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="M70" s="14" t="s">
-        <v>516</v>
+      <c r="M70" s="25" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.35">
@@ -7476,8 +7826,8 @@
       <c r="E71" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="M71" s="14" t="s">
-        <v>517</v>
+      <c r="M71" s="24" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.35">
@@ -7490,8 +7840,8 @@
       <c r="E72" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="M72" s="14" t="s">
-        <v>518</v>
+      <c r="M72" s="24" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.35">
@@ -7504,8 +7854,8 @@
       <c r="E73" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="M73" s="14" t="s">
-        <v>519</v>
+      <c r="M73" s="24" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.35">
@@ -7518,8 +7868,8 @@
       <c r="E74" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="M74" s="14" t="s">
-        <v>520</v>
+      <c r="M74" s="24" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.35">
@@ -7532,8 +7882,8 @@
       <c r="E75" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="M75" s="14" t="s">
-        <v>521</v>
+      <c r="M75" s="24" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.35">
@@ -7546,8 +7896,8 @@
       <c r="E76" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="M76" s="14" t="s">
-        <v>522</v>
+      <c r="M76" s="28" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.35">
@@ -7560,8 +7910,8 @@
       <c r="E77" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="M77" s="14" t="s">
-        <v>523</v>
+      <c r="M77" s="18" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.35">
@@ -7574,8 +7924,8 @@
       <c r="E78" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="M78" s="14" t="s">
-        <v>524</v>
+      <c r="M78" s="24" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.35">
@@ -7588,8 +7938,8 @@
       <c r="E79" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="M79" s="14" t="s">
-        <v>525</v>
+      <c r="M79" s="24" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.35">
@@ -7602,99 +7952,186 @@
       <c r="E80" s="3" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M80" s="24" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M81" s="24" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>79</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M82" s="25" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M83" s="18" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M84" s="24" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M85" s="24" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M86" s="24" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M87" s="24" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M88" s="24" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M89" s="15" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M90" s="29" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M91" s="29" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="M92" s="29" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M93" s="29" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M94" s="30" t="s">
+        <v>524</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2">
-    <cfRule type="duplicateValues" dxfId="7" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="319"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G68">
-    <cfRule type="duplicateValues" dxfId="5" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="343"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G38 G40:G41 G45:G53 G55:G56 G58:G59 G61:G62 G64:G68 G43">
-    <cfRule type="duplicateValues" dxfId="4" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G62 G64:G68">
-    <cfRule type="duplicateValues" dxfId="3" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60 G57 G54 G44 G42 G39">
-    <cfRule type="duplicateValues" dxfId="2" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M58 M61">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M59">
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M62">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64:M67">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M69 M71:M75">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M70">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M78:M81">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M82">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M84:M87">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M88">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M90:M93">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M94">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>